--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Airline_Cumulative_Statistics_2020.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Airline_Cumulative_Statistics_2020.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
   <si>
     <t>Row</t>
   </si>
@@ -25,6 +25,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Delta</t>
@@ -163,7 +166,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -186,40 +189,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
@@ -350,40 +353,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>64509463624</v>
+        <v>348731</v>
       </c>
       <c r="C5" s="0">
-        <v>117434655834</v>
+        <v>2253456</v>
       </c>
       <c r="D5" s="0">
-        <v>410654</v>
+        <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F5" s="0">
-        <v>580786</v>
+        <v>30</v>
       </c>
       <c r="G5" s="0">
-        <v>2.0299999999999998</v>
+        <v>0</v>
       </c>
       <c r="H5" s="0">
-        <v>5.6299999999999999</v>
+        <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>54.93</v>
+        <v>15.48</v>
       </c>
       <c r="J5" s="0">
-        <v>1096</v>
+        <v>442</v>
       </c>
       <c r="K5" s="0">
-        <v>6262.7600000000002</v>
+        <v>0</v>
       </c>
       <c r="L5" s="0">
-        <v>34.869999999999997</v>
+        <v>0</v>
       </c>
       <c r="M5" s="0">
-        <v>0.085999999999999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -391,40 +394,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>11434771444</v>
+        <v>66255419139</v>
       </c>
       <c r="C6" s="0">
-        <v>16946207332</v>
+        <v>120078546780</v>
       </c>
       <c r="D6" s="0">
-        <v>568665</v>
+        <v>405931</v>
       </c>
       <c r="E6" s="0">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="F6" s="0">
-        <v>88652</v>
+        <v>613227</v>
       </c>
       <c r="G6" s="0">
-        <v>2.9700000000000002</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="H6" s="0">
-        <v>7.9199999999999999</v>
+        <v>5.6299999999999999</v>
       </c>
       <c r="I6" s="0">
-        <v>67.480000000000004</v>
+        <v>55.18</v>
       </c>
       <c r="J6" s="0">
-        <v>998</v>
+        <v>1066</v>
       </c>
       <c r="K6" s="0">
-        <v>5210.4099999999999</v>
+        <v>6253.3699999999999</v>
       </c>
       <c r="L6" s="0">
-        <v>27.210000000000001</v>
+        <v>35</v>
       </c>
       <c r="M6" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="7">
@@ -432,40 +435,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>4569205024</v>
+        <v>11434771444</v>
       </c>
       <c r="C7" s="0">
-        <v>7543102763</v>
+        <v>16946207332</v>
       </c>
       <c r="D7" s="0">
-        <v>340854</v>
+        <v>568665</v>
       </c>
       <c r="E7" s="0">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="F7" s="0">
-        <v>40066</v>
+        <v>88652</v>
       </c>
       <c r="G7" s="0">
-        <v>1.8100000000000001</v>
+        <v>2.9700000000000002</v>
       </c>
       <c r="H7" s="0">
-        <v>3.8599999999999999</v>
+        <v>7.9199999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>60.57</v>
+        <v>67.480000000000004</v>
       </c>
       <c r="J7" s="0">
-        <v>837</v>
+        <v>998</v>
       </c>
       <c r="K7" s="0">
-        <v>9147.7800000000007</v>
+        <v>5210.4099999999999</v>
       </c>
       <c r="L7" s="0">
-        <v>43.399999999999999</v>
+        <v>27.210000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.10299999999999999</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="8">
@@ -473,40 +476,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>18609443820</v>
+        <v>4569205024</v>
       </c>
       <c r="C8" s="0">
-        <v>32709399297</v>
+        <v>7543102763</v>
       </c>
       <c r="D8" s="0">
-        <v>338993</v>
+        <v>340854</v>
       </c>
       <c r="E8" s="0">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F8" s="0">
-        <v>169073</v>
+        <v>40066</v>
       </c>
       <c r="G8" s="0">
-        <v>1.75</v>
+        <v>1.8100000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>5.3799999999999999</v>
+        <v>3.8599999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>56.890000000000001</v>
+        <v>60.57</v>
       </c>
       <c r="J8" s="0">
-        <v>1220</v>
+        <v>837</v>
       </c>
       <c r="K8" s="0">
-        <v>5403.6499999999996</v>
+        <v>9147.7800000000007</v>
       </c>
       <c r="L8" s="0">
-        <v>34.460000000000001</v>
+        <v>43.399999999999999</v>
       </c>
       <c r="M8" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.10299999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -514,40 +517,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>55689428774</v>
+        <v>18609443820</v>
       </c>
       <c r="C9" s="0">
-        <v>108346892246</v>
+        <v>32709399297</v>
       </c>
       <c r="D9" s="0">
-        <v>401032</v>
+        <v>338993</v>
       </c>
       <c r="E9" s="0">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F9" s="0">
-        <v>940304</v>
+        <v>169073</v>
       </c>
       <c r="G9" s="0">
-        <v>3.48</v>
+        <v>1.75</v>
       </c>
       <c r="H9" s="0">
-        <v>6.9199999999999999</v>
+        <v>5.3799999999999999</v>
       </c>
       <c r="I9" s="0">
-        <v>51.399999999999999</v>
+        <v>56.890000000000001</v>
       </c>
       <c r="J9" s="0">
-        <v>743</v>
+        <v>1220</v>
       </c>
       <c r="K9" s="0">
-        <v>4217.8000000000002</v>
+        <v>5403.6499999999996</v>
       </c>
       <c r="L9" s="0">
-        <v>27.289999999999999</v>
+        <v>34.460000000000001</v>
       </c>
       <c r="M9" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="10">
@@ -555,40 +558,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>19315111252</v>
+        <v>55689428774</v>
       </c>
       <c r="C10" s="0">
-        <v>27936759144</v>
+        <v>108346892246</v>
       </c>
       <c r="D10" s="0">
-        <v>498693</v>
+        <v>401032</v>
       </c>
       <c r="E10" s="0">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="F10" s="0">
-        <v>143251</v>
+        <v>940304</v>
       </c>
       <c r="G10" s="0">
-        <v>2.5600000000000001</v>
+        <v>3.48</v>
       </c>
       <c r="H10" s="0">
-        <v>6.8700000000000001</v>
+        <v>6.9199999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>69.140000000000001</v>
+        <v>51.399999999999999</v>
       </c>
       <c r="J10" s="0">
-        <v>1036</v>
+        <v>743</v>
       </c>
       <c r="K10" s="0">
-        <v>4158.0600000000004</v>
+        <v>4217.8000000000002</v>
       </c>
       <c r="L10" s="0">
-        <v>22.09</v>
+        <v>27.289999999999999</v>
       </c>
       <c r="M10" s="0">
-        <v>0.057000000000000002</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="11">
@@ -596,40 +599,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>2513939423</v>
+        <v>19315111252</v>
       </c>
       <c r="C11" s="0">
-        <v>4125066040</v>
+        <v>27936759144</v>
       </c>
       <c r="D11" s="0">
-        <v>331597</v>
+        <v>498693</v>
       </c>
       <c r="E11" s="0">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F11" s="0">
-        <v>18472</v>
+        <v>143251</v>
       </c>
       <c r="G11" s="0">
-        <v>1.48</v>
+        <v>2.5600000000000001</v>
       </c>
       <c r="H11" s="0">
-        <v>4.46</v>
+        <v>6.8700000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>60.939999999999998</v>
+        <v>69.140000000000001</v>
       </c>
       <c r="J11" s="0">
-        <v>1199</v>
+        <v>1036</v>
       </c>
       <c r="K11" s="0">
-        <v>4789.7200000000003</v>
+        <v>4158.0600000000004</v>
       </c>
       <c r="L11" s="0">
-        <v>25.710000000000001</v>
+        <v>22.09</v>
       </c>
       <c r="M11" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.057000000000000002</v>
       </c>
     </row>
     <row r="12">
@@ -637,40 +640,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>62458287843</v>
+        <v>2513939423</v>
       </c>
       <c r="C12" s="0">
-        <v>104531177718</v>
+        <v>4125066040</v>
       </c>
       <c r="D12" s="0">
-        <v>0</v>
+        <v>331597</v>
       </c>
       <c r="E12" s="0">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F12" s="0">
-        <v>353827</v>
+        <v>18472</v>
       </c>
       <c r="G12" s="0">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="H12" s="0">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="I12" s="0">
-        <v>59.75</v>
+        <v>60.939999999999998</v>
       </c>
       <c r="J12" s="0">
-        <v>1497</v>
+        <v>1199</v>
       </c>
       <c r="K12" s="0">
-        <v>7840.3199999999997</v>
+        <v>4789.7200000000003</v>
       </c>
       <c r="L12" s="0">
-        <v>40.950000000000003</v>
+        <v>25.710000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.095000000000000001</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -678,40 +681,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>414983325</v>
+        <v>62458287843</v>
       </c>
       <c r="C13" s="0">
-        <v>646085400</v>
+        <v>104531177718</v>
       </c>
       <c r="D13" s="0">
-        <v>174147</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="F13" s="0">
-        <v>33234</v>
+        <v>353827</v>
       </c>
       <c r="G13" s="0">
-        <v>8.9600000000000009</v>
+        <v>0</v>
       </c>
       <c r="H13" s="0">
-        <v>14.15</v>
+        <v>0</v>
       </c>
       <c r="I13" s="0">
-        <v>64.230000000000004</v>
+        <v>59.75</v>
       </c>
       <c r="J13" s="0">
-        <v>389</v>
+        <v>1497</v>
       </c>
       <c r="K13" s="0">
-        <v>482.76999999999998</v>
+        <v>7840.3199999999997</v>
       </c>
       <c r="L13" s="0">
-        <v>9.6600000000000001</v>
+        <v>40.950000000000003</v>
       </c>
       <c r="M13" s="0">
-        <v>0.039</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -719,40 +722,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>2997269011</v>
+        <v>414983325</v>
       </c>
       <c r="C14" s="0">
-        <v>5983966046</v>
+        <v>646085400</v>
       </c>
       <c r="D14" s="0">
-        <v>95392</v>
+        <v>174147</v>
       </c>
       <c r="E14" s="0">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="F14" s="0">
-        <v>210808</v>
+        <v>33234</v>
       </c>
       <c r="G14" s="0">
-        <v>3.3599999999999999</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="H14" s="0">
-        <v>4.8399999999999999</v>
+        <v>14.15</v>
       </c>
       <c r="I14" s="0">
-        <v>50.090000000000003</v>
+        <v>64.230000000000004</v>
       </c>
       <c r="J14" s="0">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="K14" s="0">
-        <v>1571.46</v>
+        <v>482.76999999999998</v>
       </c>
       <c r="L14" s="0">
-        <v>22.600000000000001</v>
+        <v>9.6600000000000001</v>
       </c>
       <c r="M14" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="15">
@@ -760,40 +763,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>4017921985</v>
+        <v>2997269011</v>
       </c>
       <c r="C15" s="0">
-        <v>6230870466</v>
+        <v>5983966046</v>
       </c>
       <c r="D15" s="0">
-        <v>48373</v>
+        <v>95392</v>
       </c>
       <c r="E15" s="0">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F15" s="0">
-        <v>171935</v>
+        <v>210808</v>
       </c>
       <c r="G15" s="0">
-        <v>1.3300000000000001</v>
+        <v>3.3599999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>2.3799999999999999</v>
+        <v>4.8399999999999999</v>
       </c>
       <c r="I15" s="0">
-        <v>64.480000000000004</v>
+        <v>50.090000000000003</v>
       </c>
       <c r="J15" s="0">
-        <v>531</v>
+        <v>404</v>
       </c>
       <c r="K15" s="0">
-        <v>1855.5699999999999</v>
+        <v>1571.46</v>
       </c>
       <c r="L15" s="0">
-        <v>27.760000000000002</v>
+        <v>22.600000000000001</v>
       </c>
       <c r="M15" s="0">
-        <v>0.090999999999999998</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="16">
@@ -801,40 +804,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>491846976</v>
+        <v>4400902375</v>
       </c>
       <c r="C16" s="0">
-        <v>801012666</v>
+        <v>6840614899</v>
       </c>
       <c r="D16" s="0">
-        <v>51281</v>
+        <v>44385</v>
       </c>
       <c r="E16" s="0">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F16" s="0">
-        <v>37699</v>
+        <v>212628</v>
       </c>
       <c r="G16" s="0">
-        <v>2.4100000000000001</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>3.6600000000000001</v>
+        <v>2.3599999999999999</v>
       </c>
       <c r="I16" s="0">
-        <v>61.399999999999999</v>
+        <v>64.329999999999998</v>
       </c>
       <c r="J16" s="0">
-        <v>399</v>
+        <v>495</v>
       </c>
       <c r="K16" s="0">
-        <v>2640.5</v>
+        <v>1839.8499999999999</v>
       </c>
       <c r="L16" s="0">
-        <v>49.689999999999998</v>
+        <v>29.109999999999999</v>
       </c>
       <c r="M16" s="0">
-        <v>0.188</v>
+        <v>0.098000000000000004</v>
       </c>
     </row>
     <row r="17">
@@ -842,40 +845,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1367770965</v>
+        <v>491846976</v>
       </c>
       <c r="C17" s="0">
-        <v>2473512264</v>
+        <v>801012666</v>
       </c>
       <c r="D17" s="0">
-        <v>223040</v>
+        <v>51281</v>
       </c>
       <c r="E17" s="0">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="F17" s="0">
-        <v>44392</v>
+        <v>37699</v>
       </c>
       <c r="G17" s="0">
-        <v>4</v>
+        <v>2.4100000000000001</v>
       </c>
       <c r="H17" s="0">
-        <v>8.4100000000000001</v>
+        <v>3.6600000000000001</v>
       </c>
       <c r="I17" s="0">
-        <v>55.299999999999997</v>
+        <v>61.399999999999999</v>
       </c>
       <c r="J17" s="0">
-        <v>733</v>
+        <v>399</v>
       </c>
       <c r="K17" s="0">
-        <v>817.98000000000002</v>
+        <v>2640.5</v>
       </c>
       <c r="L17" s="0">
-        <v>10.76</v>
+        <v>49.689999999999998</v>
       </c>
       <c r="M17" s="0">
-        <v>0.031</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="18">
@@ -883,40 +886,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>4299817607</v>
+        <v>1887749003</v>
       </c>
       <c r="C18" s="0">
-        <v>6523308419</v>
+        <v>3496575092</v>
       </c>
       <c r="D18" s="0">
-        <v>196900</v>
+        <v>160393</v>
       </c>
       <c r="E18" s="0">
         <v>76</v>
       </c>
       <c r="F18" s="0">
-        <v>139183</v>
+        <v>94780</v>
       </c>
       <c r="G18" s="0">
-        <v>4.2000000000000002</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="H18" s="0">
-        <v>8.0399999999999991</v>
+        <v>7.04</v>
       </c>
       <c r="I18" s="0">
-        <v>65.909999999999997</v>
+        <v>53.990000000000002</v>
       </c>
       <c r="J18" s="0">
-        <v>619</v>
+        <v>485</v>
       </c>
       <c r="K18" s="0">
-        <v>1409.0999999999999</v>
+        <v>1379.0799999999999</v>
       </c>
       <c r="L18" s="0">
-        <v>18.620000000000001</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="M18" s="0">
-        <v>0.058000000000000003</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -924,40 +927,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>574409931</v>
+        <v>4299817607</v>
       </c>
       <c r="C19" s="0">
-        <v>993152350</v>
+        <v>6523308419</v>
       </c>
       <c r="D19" s="0">
-        <v>0</v>
+        <v>196900</v>
       </c>
       <c r="E19" s="0">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F19" s="0">
-        <v>69034</v>
+        <v>139183</v>
       </c>
       <c r="G19" s="0">
-        <v>0</v>
+        <v>4.2000000000000002</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="I19" s="0">
-        <v>57.840000000000003</v>
+        <v>65.909999999999997</v>
       </c>
       <c r="J19" s="0">
-        <v>288</v>
+        <v>619</v>
       </c>
       <c r="K19" s="0">
-        <v>0</v>
+        <v>1411.9300000000001</v>
       </c>
       <c r="L19" s="0">
-        <v>0</v>
+        <v>18.66</v>
       </c>
       <c r="M19" s="0">
-        <v>0</v>
+        <v>0.058000000000000003</v>
       </c>
     </row>
     <row r="20">
@@ -965,40 +968,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>3542066616</v>
+        <v>574409931</v>
       </c>
       <c r="C20" s="0">
-        <v>5516038607</v>
+        <v>993152350</v>
       </c>
       <c r="D20" s="0">
-        <v>109337</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F20" s="0">
-        <v>187945</v>
+        <v>69034</v>
       </c>
       <c r="G20" s="0">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>5.9000000000000004</v>
+        <v>0</v>
       </c>
       <c r="I20" s="0">
-        <v>64.209999999999994</v>
+        <v>57.840000000000003</v>
       </c>
       <c r="J20" s="0">
-        <v>416</v>
+        <v>288</v>
       </c>
       <c r="K20" s="0">
-        <v>2014.23</v>
+        <v>0</v>
       </c>
       <c r="L20" s="0">
-        <v>28.559999999999999</v>
+        <v>0</v>
       </c>
       <c r="M20" s="0">
-        <v>0.109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1006,40 +1009,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>5082775801</v>
+        <v>3542066616</v>
       </c>
       <c r="C21" s="0">
-        <v>8885930759</v>
+        <v>5516038607</v>
       </c>
       <c r="D21" s="0">
-        <v>115883</v>
+        <v>109337</v>
       </c>
       <c r="E21" s="0">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F21" s="0">
-        <v>214926</v>
+        <v>187945</v>
       </c>
       <c r="G21" s="0">
-        <v>2.7999999999999998</v>
+        <v>3.73</v>
       </c>
       <c r="H21" s="0">
-        <v>5.2000000000000002</v>
+        <v>5.9000000000000004</v>
       </c>
       <c r="I21" s="0">
-        <v>57.200000000000003</v>
+        <v>64.209999999999994</v>
       </c>
       <c r="J21" s="0">
-        <v>556</v>
+        <v>416</v>
       </c>
       <c r="K21" s="0">
-        <v>2073.6799999999998</v>
+        <v>2014.23</v>
       </c>
       <c r="L21" s="0">
-        <v>27.870000000000001</v>
+        <v>28.559999999999999</v>
       </c>
       <c r="M21" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="22">
@@ -1047,40 +1050,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>11039774294</v>
+        <v>5082775801</v>
       </c>
       <c r="C22" s="0">
-        <v>19646811185</v>
+        <v>8885930759</v>
       </c>
       <c r="D22" s="0">
-        <v>133136</v>
+        <v>115883</v>
       </c>
       <c r="E22" s="0">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="F22" s="0">
-        <v>590871</v>
+        <v>214926</v>
       </c>
       <c r="G22" s="0">
-        <v>4</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="H22" s="0">
-        <v>6.6600000000000001</v>
+        <v>5.2000000000000002</v>
       </c>
       <c r="I22" s="0">
-        <v>56.189999999999998</v>
+        <v>57.200000000000003</v>
       </c>
       <c r="J22" s="0">
-        <v>501</v>
+        <v>556</v>
       </c>
       <c r="K22" s="0">
-        <v>2112.0900000000001</v>
+        <v>2073.6799999999998</v>
       </c>
       <c r="L22" s="0">
-        <v>32.210000000000001</v>
+        <v>27.870000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.106</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1088,39 +1091,80 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>375183124315</v>
+        <v>11039774294</v>
       </c>
       <c r="C23" s="0">
-        <v>641154635400</v>
+        <v>19646811185</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>133136</v>
       </c>
       <c r="E23" s="0">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="F23" s="0">
-        <v>4876531</v>
+        <v>590871</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H23" s="0">
-        <v>0</v>
+        <v>6.6600000000000001</v>
       </c>
       <c r="I23" s="0">
-        <v>58.520000000000003</v>
+        <v>56.189999999999998</v>
       </c>
       <c r="J23" s="0">
-        <v>849</v>
+        <v>501</v>
       </c>
       <c r="K23" s="0">
-        <v>4920.4300000000003</v>
+        <v>2112.0900000000001</v>
       </c>
       <c r="L23" s="0">
-        <v>33.520000000000003</v>
+        <v>32.210000000000001</v>
       </c>
       <c r="M23" s="0">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0">
+        <v>377832386989</v>
+      </c>
+      <c r="C24" s="0">
+        <v>645433587063</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0">
+        <v>129</v>
+      </c>
+      <c r="F24" s="0">
+        <v>5000083</v>
+      </c>
+      <c r="G24" s="0">
+        <v>0</v>
+      </c>
+      <c r="H24" s="0">
+        <v>0</v>
+      </c>
+      <c r="I24" s="0">
+        <v>58.539999999999999</v>
+      </c>
+      <c r="J24" s="0">
+        <v>837</v>
+      </c>
+      <c r="K24" s="0">
+        <v>4895.54</v>
+      </c>
+      <c r="L24" s="0">
+        <v>33.549999999999997</v>
+      </c>
+      <c r="M24" s="0">
         <v>0.086999999999999994</v>
       </c>
     </row>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Airline_Cumulative_Statistics_2020.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2020/Airline_Cumulative_Statistics_2020.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
   <si>
     <t>Row</t>
   </si>
@@ -82,6 +82,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -166,7 +178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -189,40 +201,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
@@ -687,7 +699,7 @@
         <v>104531177718</v>
       </c>
       <c r="D13" s="0">
-        <v>0</v>
+        <v>367253</v>
       </c>
       <c r="E13" s="0">
         <v>174</v>
@@ -696,10 +708,10 @@
         <v>353827</v>
       </c>
       <c r="G13" s="0">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="H13" s="0">
-        <v>0</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="I13" s="0">
         <v>59.75</v>
@@ -1132,39 +1144,203 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
+        <v>205776074655</v>
+      </c>
+      <c r="C24" s="0">
+        <v>344178252783</v>
+      </c>
+      <c r="D24" s="0">
+        <v>420920</v>
+      </c>
+      <c r="E24" s="0">
+        <v>167</v>
+      </c>
+      <c r="F24" s="0">
+        <v>1580443</v>
+      </c>
+      <c r="G24" s="0">
+        <v>1.9299999999999999</v>
+      </c>
+      <c r="H24" s="0">
+        <v>5.7300000000000004</v>
+      </c>
+      <c r="I24" s="0">
+        <v>59.789999999999999</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1177</v>
+      </c>
+      <c r="K24" s="0">
+        <v>7080.2600000000002</v>
+      </c>
+      <c r="L24" s="0">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.096000000000000002</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>96306898290</v>
+      </c>
+      <c r="C25" s="0">
+        <v>179987361608</v>
+      </c>
+      <c r="D25" s="0">
+        <v>404184</v>
+      </c>
+      <c r="E25" s="0">
+        <v>154</v>
+      </c>
+      <c r="F25" s="0">
+        <v>1292899</v>
+      </c>
+      <c r="G25" s="0">
+        <v>2.8999999999999999</v>
+      </c>
+      <c r="H25" s="0">
+        <v>6.5999999999999996</v>
+      </c>
+      <c r="I25" s="0">
+        <v>53.509999999999998</v>
+      </c>
+      <c r="J25" s="0">
+        <v>870</v>
+      </c>
+      <c r="K25" s="0">
+        <v>4673.8599999999997</v>
+      </c>
+      <c r="L25" s="0">
+        <v>29.48</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.075999999999999998</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>41017819105</v>
+      </c>
+      <c r="C26" s="0">
+        <v>61934477249</v>
+      </c>
+      <c r="D26" s="0">
+        <v>463165</v>
+      </c>
+      <c r="E26" s="0">
+        <v>185</v>
+      </c>
+      <c r="F26" s="0">
+        <v>335633</v>
+      </c>
+      <c r="G26" s="0">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="H26" s="0">
+        <v>6.5</v>
+      </c>
+      <c r="I26" s="0">
+        <v>66.230000000000004</v>
+      </c>
+      <c r="J26" s="0">
+        <v>994</v>
+      </c>
+      <c r="K26" s="0">
+        <v>4371.1700000000001</v>
+      </c>
+      <c r="L26" s="0">
+        <v>23.539999999999999</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.060999999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>34731594939</v>
+      </c>
+      <c r="C27" s="0">
+        <v>59333495423</v>
+      </c>
+      <c r="D27" s="0">
+        <v>104865</v>
+      </c>
+      <c r="E27" s="0">
+        <v>67</v>
+      </c>
+      <c r="F27" s="0">
+        <v>1791108</v>
+      </c>
+      <c r="G27" s="0">
+        <v>3.1699999999999999</v>
+      </c>
+      <c r="H27" s="0">
+        <v>5.25</v>
+      </c>
+      <c r="I27" s="0">
+        <v>58.539999999999999</v>
+      </c>
+      <c r="J27" s="0">
+        <v>482</v>
+      </c>
+      <c r="K27" s="0">
+        <v>1822.9400000000001</v>
+      </c>
+      <c r="L27" s="0">
+        <v>26.879999999999999</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.090999999999999998</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
         <v>377832386989</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C28" s="0">
         <v>645433587063</v>
       </c>
-      <c r="D24" s="0">
-        <v>0</v>
-      </c>
-      <c r="E24" s="0">
+      <c r="D28" s="0">
+        <v>328880</v>
+      </c>
+      <c r="E28" s="0">
         <v>129</v>
       </c>
-      <c r="F24" s="0">
+      <c r="F28" s="0">
         <v>5000083</v>
       </c>
-      <c r="G24" s="0">
-        <v>0</v>
-      </c>
-      <c r="H24" s="0">
-        <v>0</v>
-      </c>
-      <c r="I24" s="0">
+      <c r="G28" s="0">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="H28" s="0">
+        <v>5.8399999999999999</v>
+      </c>
+      <c r="I28" s="0">
         <v>58.539999999999999</v>
       </c>
-      <c r="J24" s="0">
+      <c r="J28" s="0">
         <v>837</v>
       </c>
-      <c r="K24" s="0">
+      <c r="K28" s="0">
         <v>4895.54</v>
       </c>
-      <c r="L24" s="0">
+      <c r="L28" s="0">
         <v>33.549999999999997</v>
       </c>
-      <c r="M24" s="0">
+      <c r="M28" s="0">
         <v>0.086999999999999994</v>
       </c>
     </row>
